--- a/XLibur.Tests/Resource/Examples/Misc/AddingDataSet.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/AddingDataSet.xlsx
@@ -456,40 +456,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:D6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.853482" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="11.424911" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="9.710625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="9.282054" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.853482" customWidth="1"/>
+    <x:col min="2" max="2" width="11.424911" customWidth="1"/>
+    <x:col min="3" max="3" width="9.710625" customWidth="1"/>
+    <x:col min="4" max="4" width="9.282054" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="B1" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C1" s="0" t="s">
+      <x:c r="C1" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D1" s="0" t="s">
+      <x:c r="D1" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
-      <x:c r="A2" s="0">
+      <x:c r="A2">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B2" s="0" t="s">
+      <x:c r="B2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="C2" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D2" s="1">
@@ -497,13 +494,13 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
-      <x:c r="A3" s="0">
+      <x:c r="A3">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
+      <x:c r="B3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="C3" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D3" s="1">
@@ -511,13 +508,13 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
-      <x:c r="A4" s="0">
+      <x:c r="A4">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
+      <x:c r="B4" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="C4" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D4" s="1">
@@ -525,13 +522,13 @@
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
-      <x:c r="A5" s="0">
+      <x:c r="A5">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
+      <x:c r="B5" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="s">
+      <x:c r="C5" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D5" s="1">
@@ -539,13 +536,13 @@
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
-      <x:c r="A6" s="0">
+      <x:c r="A6">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
+      <x:c r="B6" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s">
+      <x:c r="C6" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D6" s="1">
@@ -553,10 +550,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId7"/>
   </x:tableParts>
@@ -565,40 +559,37 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:D6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.853482" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="11.424911" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="9.710625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="9.282054" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.853482" customWidth="1"/>
+    <x:col min="2" max="2" width="11.424911" customWidth="1"/>
+    <x:col min="3" max="3" width="9.710625" customWidth="1"/>
+    <x:col min="4" max="4" width="9.282054" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="B1" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C1" s="0" t="s">
+      <x:c r="C1" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D1" s="0" t="s">
+      <x:c r="D1" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
-      <x:c r="A2" s="0">
+      <x:c r="A2">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B2" s="0" t="s">
+      <x:c r="B2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="C2" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D2" s="1">
@@ -606,13 +597,13 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
-      <x:c r="A3" s="0">
+      <x:c r="A3">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
+      <x:c r="B3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="C3" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D3" s="1">
@@ -620,13 +611,13 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
-      <x:c r="A4" s="0">
+      <x:c r="A4">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
+      <x:c r="B4" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="C4" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D4" s="1">
@@ -634,13 +625,13 @@
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
-      <x:c r="A5" s="0">
+      <x:c r="A5">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
+      <x:c r="B5" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="s">
+      <x:c r="C5" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D5" s="1">
@@ -648,13 +639,13 @@
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
-      <x:c r="A6" s="0">
+      <x:c r="A6">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
+      <x:c r="B6" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s">
+      <x:c r="C6" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D6" s="1">
@@ -662,10 +653,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId8"/>
   </x:tableParts>
@@ -674,40 +662,37 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:D6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.853482" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="11.424911" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="9.710625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="9.282054" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.853482" customWidth="1"/>
+    <x:col min="2" max="2" width="11.424911" customWidth="1"/>
+    <x:col min="3" max="3" width="9.710625" customWidth="1"/>
+    <x:col min="4" max="4" width="9.282054" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">
-      <x:c r="A1" s="0" t="s">
+      <x:c r="A1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="B1" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C1" s="0" t="s">
+      <x:c r="C1" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D1" s="0" t="s">
+      <x:c r="D1" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
-      <x:c r="A2" s="0">
+      <x:c r="A2">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B2" s="0" t="s">
+      <x:c r="B2" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="C2" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D2" s="1">
@@ -715,13 +700,13 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
-      <x:c r="A3" s="0">
+      <x:c r="A3">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
+      <x:c r="B3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="C3" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D3" s="1">
@@ -729,13 +714,13 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
-      <x:c r="A4" s="0">
+      <x:c r="A4">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
+      <x:c r="B4" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="C4" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D4" s="1">
@@ -743,13 +728,13 @@
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
-      <x:c r="A5" s="0">
+      <x:c r="A5">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
+      <x:c r="B5" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="s">
+      <x:c r="C5" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D5" s="1">
@@ -757,13 +742,13 @@
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
-      <x:c r="A6" s="0">
+      <x:c r="A6">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
+      <x:c r="B6" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s">
+      <x:c r="C6" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D6" s="1">
@@ -771,10 +756,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
     <x:tablePart r:id="rId9"/>
   </x:tableParts>

--- a/XLibur.Tests/Resource/Examples/Misc/AddingDataSet.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/AddingDataSet.xlsx
@@ -459,10 +459,10 @@
   <x:dimension ref="A1:D6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.853482" customWidth="1"/>
-    <x:col min="2" max="2" width="11.424911" customWidth="1"/>
-    <x:col min="3" max="3" width="9.710625" customWidth="1"/>
-    <x:col min="4" max="4" width="9.282054" customWidth="1"/>
+    <x:col min="1" max="1" width="9.567768" customWidth="1"/>
+    <x:col min="2" max="2" width="11.139196" customWidth="1"/>
+    <x:col min="3" max="3" width="9.424911" customWidth="1"/>
+    <x:col min="4" max="4" width="8.996339" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">
@@ -562,10 +562,10 @@
   <x:dimension ref="A1:D6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.853482" customWidth="1"/>
-    <x:col min="2" max="2" width="11.424911" customWidth="1"/>
-    <x:col min="3" max="3" width="9.710625" customWidth="1"/>
-    <x:col min="4" max="4" width="9.282054" customWidth="1"/>
+    <x:col min="1" max="1" width="9.567768" customWidth="1"/>
+    <x:col min="2" max="2" width="11.139196" customWidth="1"/>
+    <x:col min="3" max="3" width="9.424911" customWidth="1"/>
+    <x:col min="4" max="4" width="8.996339" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">
@@ -665,10 +665,10 @@
   <x:dimension ref="A1:D6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.853482" customWidth="1"/>
-    <x:col min="2" max="2" width="11.424911" customWidth="1"/>
-    <x:col min="3" max="3" width="9.710625" customWidth="1"/>
-    <x:col min="4" max="4" width="9.282054" customWidth="1"/>
+    <x:col min="1" max="1" width="9.567768" customWidth="1"/>
+    <x:col min="2" max="2" width="11.139196" customWidth="1"/>
+    <x:col min="3" max="3" width="9.424911" customWidth="1"/>
+    <x:col min="4" max="4" width="8.996339" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">

--- a/XLibur.Tests/Resource/Examples/Misc/AddingDataSet.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/AddingDataSet.xlsx
@@ -459,10 +459,10 @@
   <x:dimension ref="A1:D6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.567768" customWidth="1"/>
-    <x:col min="2" max="2" width="11.139196" customWidth="1"/>
-    <x:col min="3" max="3" width="9.424911" customWidth="1"/>
-    <x:col min="4" max="4" width="8.996339" customWidth="1"/>
+    <x:col min="1" max="1" width="9.571429" customWidth="1"/>
+    <x:col min="2" max="2" width="11.142857" customWidth="1"/>
+    <x:col min="3" max="3" width="9.428571" customWidth="1"/>
+    <x:col min="4" max="4" width="9" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">
@@ -562,10 +562,10 @@
   <x:dimension ref="A1:D6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.567768" customWidth="1"/>
-    <x:col min="2" max="2" width="11.139196" customWidth="1"/>
-    <x:col min="3" max="3" width="9.424911" customWidth="1"/>
-    <x:col min="4" max="4" width="8.996339" customWidth="1"/>
+    <x:col min="1" max="1" width="9.571429" customWidth="1"/>
+    <x:col min="2" max="2" width="11.142857" customWidth="1"/>
+    <x:col min="3" max="3" width="9.428571" customWidth="1"/>
+    <x:col min="4" max="4" width="9" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">
@@ -665,10 +665,10 @@
   <x:dimension ref="A1:D6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.567768" customWidth="1"/>
-    <x:col min="2" max="2" width="11.139196" customWidth="1"/>
-    <x:col min="3" max="3" width="9.424911" customWidth="1"/>
-    <x:col min="4" max="4" width="8.996339" customWidth="1"/>
+    <x:col min="1" max="1" width="9.571429" customWidth="1"/>
+    <x:col min="2" max="2" width="11.142857" customWidth="1"/>
+    <x:col min="3" max="3" width="9.428571" customWidth="1"/>
+    <x:col min="4" max="4" width="9" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:4">
